--- a/fuction_ensemble/redes-ensemble-s/Teste05/content/results/metrics_9_3.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste05/content/results/metrics_9_3.xlsx
@@ -513,661 +513,661 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_9_3_0</t>
+          <t>model_9_3_24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9998460861655027</v>
+        <v>0.9999998297916656</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6670980992640219</v>
+        <v>0.6981921017275976</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9999984666948489</v>
+        <v>0.9999997687355866</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999594818562678</v>
+        <v>0.9999992408087114</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999860533536195</v>
+        <v>0.9999995622461744</v>
       </c>
       <c r="G2" t="n">
-        <v>9.136990088905362e-05</v>
+        <v>1.010430199533477e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1976249488902018</v>
+        <v>0.1791662058368556</v>
       </c>
       <c r="I2" t="n">
-        <v>6.166989431801787e-07</v>
+        <v>1.397057992604021e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.23426178234373e-05</v>
+        <v>3.907922916231321e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.147965838330874e-05</v>
+        <v>2.652490454417671e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002157039093563412</v>
+        <v>9.821809564892923e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>0.009558760426386552</v>
+        <v>0.0003178726473815382</v>
       </c>
       <c r="N2" t="n">
-        <v>1.000082087378398</v>
+        <v>1.000000090777778</v>
       </c>
       <c r="O2" t="n">
-        <v>0.009965696647099729</v>
+        <v>0.0003314051440676629</v>
       </c>
       <c r="P2" t="n">
-        <v>156.6011888913504</v>
+        <v>170.2154389413195</v>
       </c>
       <c r="Q2" t="n">
-        <v>240.7036208072562</v>
+        <v>254.3178708572253</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_9_3_1</t>
+          <t>model_9_3_23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9998727405313506</v>
+        <v>0.9999998239004986</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6663505529762337</v>
+        <v>0.6981662232309322</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9999901897932283</v>
+        <v>0.9999997673153695</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999547905295876</v>
+        <v>0.9999992456459236</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999824597893181</v>
+        <v>0.9999995635928595</v>
       </c>
       <c r="G3" t="n">
-        <v>7.55467179131165e-05</v>
+        <v>1.045402711569505e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>0.198068724658951</v>
+        <v>0.179181568430369</v>
       </c>
       <c r="I3" t="n">
-        <v>3.94568826961059e-06</v>
+        <v>1.405637459845561e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.492952110789514e-05</v>
+        <v>3.883023457552941e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.443756592840027e-05</v>
+        <v>2.644330458699251e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002153372028939342</v>
+        <v>0.0001023644370023874</v>
       </c>
       <c r="M3" t="n">
-        <v>0.008691761496561931</v>
+        <v>0.0003233268797315659</v>
       </c>
       <c r="N3" t="n">
-        <v>1.000067871716613</v>
+        <v>1.000000093919734</v>
       </c>
       <c r="O3" t="n">
-        <v>0.009061787777897273</v>
+        <v>0.0003370915743806488</v>
       </c>
       <c r="P3" t="n">
-        <v>156.9815186255374</v>
+        <v>170.147386939709</v>
       </c>
       <c r="Q3" t="n">
-        <v>241.0839505414433</v>
+        <v>254.2498188556148</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_9_3_2</t>
+          <t>model_9_3_22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9998931626668627</v>
+        <v>0.999999816262174</v>
       </c>
       <c r="C4" t="n">
-        <v>0.665641228233475</v>
+        <v>0.6981391755440076</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9999747942995051</v>
+        <v>0.9999997658247525</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9999497260647445</v>
+        <v>0.9999992493949994</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9999770019316615</v>
+        <v>0.9999995644422573</v>
       </c>
       <c r="G4" t="n">
-        <v>6.342325608279671e-05</v>
+        <v>1.090747105730315e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>0.198489810467486</v>
+        <v>0.1791976251057267</v>
       </c>
       <c r="I4" t="n">
-        <v>1.013779210610747e-05</v>
+        <v>1.414642211495624e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>2.772218118670046e-05</v>
+        <v>3.863725159666094e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>1.892999655957252e-05</v>
+        <v>2.639183685580859e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002162176319838427</v>
+        <v>0.0001071690884302813</v>
       </c>
       <c r="M4" t="n">
-        <v>0.007963871927824851</v>
+        <v>0.0003302646069033609</v>
       </c>
       <c r="N4" t="n">
-        <v>1.000056979911007</v>
+        <v>1.000000097993507</v>
       </c>
       <c r="O4" t="n">
-        <v>0.008302910443279927</v>
+        <v>0.0003443246549612222</v>
       </c>
       <c r="P4" t="n">
-        <v>157.3313598971905</v>
+        <v>170.0624655428155</v>
       </c>
       <c r="Q4" t="n">
-        <v>241.4337918130964</v>
+        <v>254.1648974587214</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_9_3_3</t>
+          <t>model_9_3_21</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.999908431433294</v>
+        <v>0.9999998071623867</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6649679982834378</v>
+        <v>0.6981089437627376</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9999527392369973</v>
+        <v>0.9999997640486106</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9999442490143748</v>
+        <v>0.9999992552030239</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9999697788010716</v>
+        <v>0.9999995659345782</v>
       </c>
       <c r="G5" t="n">
-        <v>5.435905675281127e-05</v>
+        <v>1.144767374272968e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1988894688478477</v>
+        <v>0.1792155719970335</v>
       </c>
       <c r="I5" t="n">
-        <v>1.900839019311647e-05</v>
+        <v>1.425371804915709e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>3.074235022550713e-05</v>
+        <v>3.833828462813001e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>2.487544533388366e-05</v>
+        <v>2.630141235844498e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002182653096018269</v>
+        <v>0.0001123583616075617</v>
       </c>
       <c r="M5" t="n">
-        <v>0.00737285946921622</v>
+        <v>0.0003383441109688431</v>
       </c>
       <c r="N5" t="n">
-        <v>1.00004883656891</v>
+        <v>1.000000102846727</v>
       </c>
       <c r="O5" t="n">
-        <v>0.007686737360743877</v>
+        <v>0.0003527481202416511</v>
       </c>
       <c r="P5" t="n">
-        <v>157.6397986413867</v>
+        <v>169.9657884023341</v>
       </c>
       <c r="Q5" t="n">
-        <v>241.7422305572925</v>
+        <v>254.06822031824</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_9_3_4</t>
+          <t>model_9_3_20</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9999194256999017</v>
+        <v>0.9999997954954666</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6643294947778053</v>
+        <v>0.698075385800605</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9999244669274018</v>
+        <v>0.9999997636295979</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9999383353674663</v>
+        <v>0.99999925810551</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9999608904023419</v>
+        <v>0.9999995672262034</v>
       </c>
       <c r="G6" t="n">
-        <v>4.783238516688162e-05</v>
+        <v>1.214027251618543e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1992685121107064</v>
+        <v>0.179235493452984</v>
       </c>
       <c r="I6" t="n">
-        <v>3.037957970230914e-05</v>
+        <v>1.427903042476343e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>3.400326843766804e-05</v>
+        <v>3.818887969693157e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>3.219159706005257e-05</v>
+        <v>2.622314865318484e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002213699843358016</v>
+        <v>0.0001181879640711349</v>
       </c>
       <c r="M6" t="n">
-        <v>0.006916096092947352</v>
+        <v>0.0003484289384678808</v>
       </c>
       <c r="N6" t="n">
-        <v>1.000042972960052</v>
+        <v>1.000000109069084</v>
       </c>
       <c r="O6" t="n">
-        <v>0.007210528621916706</v>
+        <v>0.0003632622797257936</v>
       </c>
       <c r="P6" t="n">
-        <v>157.8956152678487</v>
+        <v>169.8483050215635</v>
       </c>
       <c r="Q6" t="n">
-        <v>241.9980471837545</v>
+        <v>253.9507369374693</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_9_3_5</t>
+          <t>model_9_3_19</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9999268778976446</v>
+        <v>0.9999997816560342</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6637242010571048</v>
+        <v>0.6980396230555068</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9998904570692172</v>
+        <v>0.9999997625990958</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9999320025520559</v>
+        <v>0.9999992653431281</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9999504601409049</v>
+        <v>0.999999569608402</v>
       </c>
       <c r="G7" t="n">
-        <v>4.340843866852367e-05</v>
+        <v>1.296184100693584e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1996278406106414</v>
+        <v>0.1792567237633443</v>
       </c>
       <c r="I7" t="n">
-        <v>4.405842476766571e-05</v>
+        <v>1.434128259096018e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>3.749532561074693e-05</v>
+        <v>3.781632466705306e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>4.077687518920632e-05</v>
+        <v>2.607880362900662e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002253807239492328</v>
+        <v>0.0001245507648852602</v>
       </c>
       <c r="M7" t="n">
-        <v>0.006588508076076379</v>
+        <v>0.0003600255686327826</v>
       </c>
       <c r="N7" t="n">
-        <v>1.00003899845459</v>
+        <v>1.000000116450115</v>
       </c>
       <c r="O7" t="n">
-        <v>0.006868994504966855</v>
+        <v>0.0003753526024451491</v>
       </c>
       <c r="P7" t="n">
-        <v>158.0897133927838</v>
+        <v>169.717342020225</v>
       </c>
       <c r="Q7" t="n">
-        <v>242.1921453086896</v>
+        <v>253.8197739361308</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_9_3_6</t>
+          <t>model_9_3_18</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.999931392716385</v>
+        <v>0.9999997641766222</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6631514367868485</v>
+        <v>0.698000163307597</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9998512329795725</v>
+        <v>0.999999761109779</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9999252646003635</v>
+        <v>0.9999992714403474</v>
       </c>
       <c r="F8" t="n">
-        <v>0.999938620033577</v>
+        <v>0.9999995713670543</v>
       </c>
       <c r="G8" t="n">
-        <v>4.072824723420715e-05</v>
+        <v>1.399949441101018e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1999678582235938</v>
+        <v>0.179280148774276</v>
       </c>
       <c r="I8" t="n">
-        <v>5.983444600742513e-05</v>
+        <v>1.443125155554934e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>4.121078406250592e-05</v>
+        <v>3.75024714493932e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>5.052261503496552e-05</v>
+        <v>2.597224125839232e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002301769415552966</v>
+        <v>0.000131625453770347</v>
       </c>
       <c r="M8" t="n">
-        <v>0.006381868631851265</v>
+        <v>0.0003741589823993295</v>
       </c>
       <c r="N8" t="n">
-        <v>1.000036590551261</v>
+        <v>1.000000125772468</v>
       </c>
       <c r="O8" t="n">
-        <v>0.00665355799179846</v>
+        <v>0.0003900877048959377</v>
       </c>
       <c r="P8" t="n">
-        <v>158.2171773420166</v>
+        <v>169.563319056977</v>
       </c>
       <c r="Q8" t="n">
-        <v>242.3196092579224</v>
+        <v>253.6657509728828</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_9_3_7</t>
+          <t>model_9_3_17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9999334733921043</v>
+        <v>0.9999997422853026</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6626100456891979</v>
+        <v>0.6979591184011363</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9998073021427912</v>
+        <v>0.9999997597809628</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9999181498099802</v>
+        <v>0.9999992771991305</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9999255037566853</v>
+        <v>0.9999995732395301</v>
       </c>
       <c r="G9" t="n">
-        <v>3.949306824671282e-05</v>
+        <v>1.529905770546959e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2002892513660369</v>
+        <v>0.1793045148037987</v>
       </c>
       <c r="I9" t="n">
-        <v>7.750353203125662e-05</v>
+        <v>1.451152474750894e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>4.513403986311297e-05</v>
+        <v>3.720603916497914e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>6.131878594718479e-05</v>
+        <v>2.585878195624404e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002356257688729158</v>
+        <v>0.0001395124597546706</v>
       </c>
       <c r="M9" t="n">
-        <v>0.006284351060110567</v>
+        <v>0.0003911400990114615</v>
       </c>
       <c r="N9" t="n">
-        <v>1.000035480857544</v>
+        <v>1.000000137447839</v>
       </c>
       <c r="O9" t="n">
-        <v>0.006551888895139558</v>
+        <v>0.0004077917427980055</v>
       </c>
       <c r="P9" t="n">
-        <v>158.2787707777638</v>
+        <v>169.3857790106568</v>
       </c>
       <c r="Q9" t="n">
-        <v>242.3812026936696</v>
+        <v>253.4882109265626</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_9_3_8</t>
+          <t>model_9_3_16</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9999335652351772</v>
+        <v>0.9999997153671384</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6620997374572228</v>
+        <v>0.6979147794500993</v>
       </c>
       <c r="D10" t="n">
-        <v>0.99975938901214</v>
+        <v>0.9999997583276143</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9999107312693413</v>
+        <v>0.9999992836176199</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9999113126259439</v>
+        <v>0.9999995752413589</v>
       </c>
       <c r="G10" t="n">
-        <v>3.943854623124546e-05</v>
+        <v>1.689703621697237e-07</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2005921923767051</v>
+        <v>0.1793308363204772</v>
       </c>
       <c r="I10" t="n">
-        <v>9.677430602914042e-05</v>
+        <v>1.459932087672969e-07</v>
       </c>
       <c r="J10" t="n">
-        <v>4.922479040185522e-05</v>
+        <v>3.687564862778981e-07</v>
       </c>
       <c r="K10" t="n">
-        <v>7.299968245367258e-05</v>
+        <v>2.573748475225976e-07</v>
       </c>
       <c r="L10" t="n">
-        <v>0.002415383362086059</v>
+        <v>0.0001483383591100587</v>
       </c>
       <c r="M10" t="n">
-        <v>0.006280011642604292</v>
+        <v>0.0004110600469149534</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000035431874572</v>
+        <v>1.000000151804193</v>
       </c>
       <c r="O10" t="n">
-        <v>0.006547364739646208</v>
+        <v>0.0004285597241237258</v>
       </c>
       <c r="P10" t="n">
-        <v>158.2815337783435</v>
+        <v>169.1870850183591</v>
       </c>
       <c r="Q10" t="n">
-        <v>242.3839656942493</v>
+        <v>253.289516934265</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_9_3_9</t>
+          <t>model_9_3_15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9999320251306083</v>
+        <v>0.999999682317751</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6616194982783119</v>
+        <v>0.6978668921874236</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9997080215677445</v>
+        <v>0.9999997565296687</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9999030478153176</v>
+        <v>0.9999992923767874</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9998961891345218</v>
+        <v>0.9999995780656313</v>
       </c>
       <c r="G11" t="n">
-        <v>4.035281883234638e-05</v>
+        <v>1.885899061529014e-07</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2008772830985589</v>
+        <v>0.1793592642682236</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0001174344131509099</v>
+        <v>1.470793397427079e-07</v>
       </c>
       <c r="J11" t="n">
-        <v>5.346162015277956e-05</v>
+        <v>3.642477212438167e-07</v>
       </c>
       <c r="K11" t="n">
-        <v>8.544801665184471e-05</v>
+        <v>2.556635304932623e-07</v>
       </c>
       <c r="L11" t="n">
-        <v>0.002478325215759848</v>
+        <v>0.0001579946466459145</v>
       </c>
       <c r="M11" t="n">
-        <v>0.006352386861042578</v>
+        <v>0.0004342693935253801</v>
       </c>
       <c r="N11" t="n">
-        <v>1.000036253263676</v>
+        <v>1.000000169430533</v>
       </c>
       <c r="O11" t="n">
-        <v>0.006622821120970768</v>
+        <v>0.0004527571406693292</v>
       </c>
       <c r="P11" t="n">
-        <v>158.2356986123013</v>
+        <v>168.9673819760945</v>
       </c>
       <c r="Q11" t="n">
-        <v>242.3381305282072</v>
+        <v>253.0698138920004</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_9_3_10</t>
+          <t>model_9_3_14</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9999291833832771</v>
+        <v>0.9999996416298749</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6611690972278779</v>
+        <v>0.6978154091566379</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9996540310974434</v>
+        <v>0.9999997550852899</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9998951808678175</v>
+        <v>0.9999993037553803</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9998803631039639</v>
+        <v>0.9999995821787716</v>
       </c>
       <c r="G12" t="n">
-        <v>4.203980280527689e-05</v>
+        <v>2.127439870542867e-07</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2011446606184088</v>
+        <v>0.1793898268192491</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0001391495074699388</v>
+        <v>1.479518824716534e-07</v>
       </c>
       <c r="J12" t="n">
-        <v>5.779963234290686e-05</v>
+        <v>3.583906119075855e-07</v>
       </c>
       <c r="K12" t="n">
-        <v>9.847461956489667e-05</v>
+        <v>2.531712471896195e-07</v>
       </c>
       <c r="L12" t="n">
-        <v>0.002543639245900043</v>
+        <v>0.0001687183581990204</v>
       </c>
       <c r="M12" t="n">
-        <v>0.006483810824297459</v>
+        <v>0.0004612417880616268</v>
       </c>
       <c r="N12" t="n">
-        <v>1.000037768862252</v>
+        <v>1.000000191130733</v>
       </c>
       <c r="O12" t="n">
-        <v>0.006759840074426517</v>
+        <v>0.0004808778058815379</v>
       </c>
       <c r="P12" t="n">
-        <v>158.1537874052234</v>
+        <v>168.7263526657138</v>
       </c>
       <c r="Q12" t="n">
-        <v>242.2562193211292</v>
+        <v>252.8287845816197</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_9_3_11</t>
+          <t>model_9_3_13</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9999253118733249</v>
+        <v>0.9999995914760405</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6607476385336879</v>
+        <v>0.6977597784047596</v>
       </c>
       <c r="D13" t="n">
-        <v>0.999598058785075</v>
+        <v>0.9999997537771124</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9998871991079217</v>
+        <v>0.9999993181688386</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9998640147420429</v>
+        <v>0.9999995876488875</v>
       </c>
       <c r="G13" t="n">
-        <v>4.433809835343212e-05</v>
+        <v>2.425174697004787e-07</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2013948567053477</v>
+        <v>0.1794228516366874</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0001616617033363122</v>
+        <v>1.487421466856366e-07</v>
       </c>
       <c r="J13" t="n">
-        <v>6.220095467616979e-05</v>
+        <v>3.509713113065444e-07</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0001119311599301559</v>
+        <v>2.498567289960904e-07</v>
       </c>
       <c r="L13" t="n">
-        <v>0.00261020331659229</v>
+        <v>0.0001805585418730123</v>
       </c>
       <c r="M13" t="n">
-        <v>0.006658685932932422</v>
+        <v>0.0004924606275637461</v>
       </c>
       <c r="N13" t="n">
-        <v>1.00003983366756</v>
+        <v>1.000000217879445</v>
       </c>
       <c r="O13" t="n">
-        <v>0.006942159978477452</v>
+        <v>0.0005134256960131693</v>
       </c>
       <c r="P13" t="n">
-        <v>158.04733248506</v>
+        <v>168.4643841783233</v>
       </c>
       <c r="Q13" t="n">
-        <v>242.1497644009659</v>
+        <v>252.5668160942292</v>
       </c>
     </row>
     <row r="14">
@@ -1177,712 +1177,712 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9999206490299788</v>
+        <v>0.9999995300566737</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6603545070721373</v>
+        <v>0.69770087545883</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9995407988868003</v>
+        <v>0.9999997536619606</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9998791780622545</v>
+        <v>0.9999993350095467</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9998473382356359</v>
+        <v>0.9999995946591054</v>
       </c>
       <c r="G14" t="n">
-        <v>4.710616358801728e-05</v>
+        <v>2.789786589282415e-07</v>
       </c>
       <c r="H14" t="n">
-        <v>0.201628236523319</v>
+        <v>0.179457818969866</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0001846917692868565</v>
+        <v>1.488117094160514e-07</v>
       </c>
       <c r="J14" t="n">
-        <v>6.662394006933476e-05</v>
+        <v>3.423025883281643e-07</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0001256578001097715</v>
+        <v>2.456090137550772e-07</v>
       </c>
       <c r="L14" t="n">
-        <v>0.002676977773391994</v>
+        <v>0.0001935199911336757</v>
       </c>
       <c r="M14" t="n">
-        <v>0.00686339300841918</v>
+        <v>0.0005281843039396774</v>
       </c>
       <c r="N14" t="n">
-        <v>1.000042320517345</v>
+        <v>1.000000250636441</v>
       </c>
       <c r="O14" t="n">
-        <v>0.007155581857969745</v>
+        <v>0.0005506702032506285</v>
       </c>
       <c r="P14" t="n">
-        <v>157.9262134075244</v>
+        <v>168.1842610986945</v>
       </c>
       <c r="Q14" t="n">
-        <v>242.0286453234303</v>
+        <v>252.2866930146004</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_9_3_13</t>
+          <t>model_9_3_11</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9999154029557665</v>
+        <v>0.9999994539282884</v>
       </c>
       <c r="C15" t="n">
-        <v>0.65998897762296</v>
+        <v>0.6976375569869677</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9994829334873071</v>
+        <v>0.9999997543154439</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9998711888842545</v>
+        <v>0.9999993535651364</v>
       </c>
       <c r="F15" t="n">
-        <v>0.999830525004431</v>
+        <v>0.9999996030363802</v>
       </c>
       <c r="G15" t="n">
-        <v>5.022045985899721e-05</v>
+        <v>3.241717571027358e-07</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2018452305944006</v>
+        <v>0.179495407549979</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0002079653692535448</v>
+        <v>1.484169430332951e-07</v>
       </c>
       <c r="J15" t="n">
-        <v>7.102935291244832e-05</v>
+        <v>3.327511333905844e-07</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0001394969801739172</v>
+        <v>2.405329549259799e-07</v>
       </c>
       <c r="L15" t="n">
-        <v>0.002743090102631976</v>
+        <v>0.0002079184015681763</v>
       </c>
       <c r="M15" t="n">
-        <v>0.007086639532175826</v>
+        <v>0.0005693608320764046</v>
       </c>
       <c r="N15" t="n">
-        <v>1.000045118423591</v>
+        <v>1.000000291238246</v>
       </c>
       <c r="O15" t="n">
-        <v>0.007388332448426725</v>
+        <v>0.0005935997014373003</v>
       </c>
       <c r="P15" t="n">
-        <v>157.7981760947742</v>
+        <v>167.883984694201</v>
       </c>
       <c r="Q15" t="n">
-        <v>241.9006080106801</v>
+        <v>251.9864166101069</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_9_3_14</t>
+          <t>model_9_3_10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9999097519309386</v>
+        <v>0.9999993599834806</v>
       </c>
       <c r="C16" t="n">
-        <v>0.659650001785798</v>
+        <v>0.6975719162238785</v>
       </c>
       <c r="D16" t="n">
-        <v>0.999425090027667</v>
+        <v>0.9999997545275607</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9998633015485899</v>
+        <v>0.9999993749909217</v>
       </c>
       <c r="F16" t="n">
-        <v>0.99981375014408</v>
+        <v>0.9999996121585717</v>
       </c>
       <c r="G16" t="n">
-        <v>5.357515230849136e-05</v>
+        <v>3.799414532409348e-07</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2020464612943337</v>
+        <v>0.1795343747424821</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0002312301449596919</v>
+        <v>1.482888041935946e-07</v>
       </c>
       <c r="J16" t="n">
-        <v>7.537860759605241e-05</v>
+        <v>3.21722250555473e-07</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0001533045767102082</v>
+        <v>2.350055273745338e-07</v>
       </c>
       <c r="L16" t="n">
-        <v>0.002807798545535835</v>
+        <v>0.0002237979066443365</v>
       </c>
       <c r="M16" t="n">
-        <v>0.007319504922362671</v>
+        <v>0.0006163939107753538</v>
       </c>
       <c r="N16" t="n">
-        <v>1.0000481323035</v>
+        <v>1.000000341342144</v>
       </c>
       <c r="O16" t="n">
-        <v>0.007631111400371634</v>
+        <v>0.0006426350756683585</v>
       </c>
       <c r="P16" t="n">
-        <v>157.6688503474127</v>
+        <v>167.5664973330293</v>
       </c>
       <c r="Q16" t="n">
-        <v>241.7712822633186</v>
+        <v>251.6689292489351</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_9_3_15</t>
+          <t>model_9_3_9</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9999038435225108</v>
+        <v>0.9999992440166625</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6593363950223555</v>
+        <v>0.697502848259933</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9993678050754462</v>
+        <v>0.9999997562030648</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9998555759813847</v>
+        <v>0.9999994028050804</v>
       </c>
       <c r="F17" t="n">
-        <v>0.999797166836345</v>
+        <v>0.9999996247271247</v>
       </c>
       <c r="G17" t="n">
-        <v>5.708263878112327e-05</v>
+        <v>4.487843659203127e-07</v>
       </c>
       <c r="H17" t="n">
-        <v>0.20223263181622</v>
+        <v>0.1795753764694608</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0002542702876663495</v>
+        <v>1.472766396994317e-07</v>
       </c>
       <c r="J17" t="n">
-        <v>7.963865950455638e-05</v>
+        <v>3.074049645762184e-07</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0001669545039018561</v>
+        <v>2.27389839060706e-07</v>
       </c>
       <c r="L17" t="n">
-        <v>0.002870787612969447</v>
+        <v>0.0002414028434851934</v>
       </c>
       <c r="M17" t="n">
-        <v>0.007555305340032477</v>
+        <v>0.0006699137003527489</v>
       </c>
       <c r="N17" t="n">
-        <v>1.000051283454661</v>
+        <v>1.000000403191113</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0078769503299958</v>
+        <v>0.000698433313489301</v>
       </c>
       <c r="P17" t="n">
-        <v>157.5420210738041</v>
+        <v>167.2334466372762</v>
       </c>
       <c r="Q17" t="n">
-        <v>241.6444529897099</v>
+        <v>251.3358785531821</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_9_3_16</t>
+          <t>model_9_3_8</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9998978157625915</v>
+        <v>0.999999100721095</v>
       </c>
       <c r="C18" t="n">
-        <v>0.659047354054021</v>
+        <v>0.6974312099394874</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9993116841692179</v>
+        <v>0.9999997575690464</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9998480574116906</v>
+        <v>0.9999994322677458</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9997809370166093</v>
+        <v>0.999999638082251</v>
       </c>
       <c r="G18" t="n">
-        <v>6.066097745490761e-05</v>
+        <v>5.338508048548208e-07</v>
       </c>
       <c r="H18" t="n">
-        <v>0.202404219020943</v>
+        <v>0.1796179040710916</v>
       </c>
       <c r="I18" t="n">
-        <v>0.000276842248333108</v>
+        <v>1.464514563473783e-07</v>
       </c>
       <c r="J18" t="n">
-        <v>8.378456831925705e-05</v>
+        <v>2.922391128507752e-07</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0001803134707175822</v>
+        <v>2.192975408639749e-07</v>
       </c>
       <c r="L18" t="n">
-        <v>0.00293127093821928</v>
+        <v>0.0002607407999548354</v>
       </c>
       <c r="M18" t="n">
-        <v>0.007788515741455981</v>
+        <v>0.0007306509459754505</v>
       </c>
       <c r="N18" t="n">
-        <v>1.000054498259951</v>
+        <v>1.000000479615416</v>
       </c>
       <c r="O18" t="n">
-        <v>0.008120088981019985</v>
+        <v>0.0007617562694015923</v>
       </c>
       <c r="P18" t="n">
-        <v>157.4204198843377</v>
+        <v>166.886298857362</v>
       </c>
       <c r="Q18" t="n">
-        <v>241.5228518002435</v>
+        <v>250.9887307732678</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_9_3_17</t>
+          <t>model_9_3_7</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9998917710875823</v>
+        <v>0.9999989234160824</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6587814356654698</v>
+        <v>0.6973564466833526</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9992570901791845</v>
+        <v>0.9999997590984049</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9998408149034507</v>
+        <v>0.9999994662163698</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9997651731107914</v>
+        <v>0.9999996531857462</v>
       </c>
       <c r="G19" t="n">
-        <v>6.424935765669685e-05</v>
+        <v>6.391067194717683e-07</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2025620796634633</v>
+        <v>0.1796622867695377</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0002988000797099559</v>
+        <v>1.455275776563557e-07</v>
       </c>
       <c r="J19" t="n">
-        <v>8.777825062503722e-05</v>
+        <v>2.747641222985249e-07</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0001932889379832265</v>
+        <v>2.101458499774403e-07</v>
       </c>
       <c r="L19" t="n">
-        <v>0.002988883354625946</v>
+        <v>0.0002822682765715924</v>
       </c>
       <c r="M19" t="n">
-        <v>0.008015569702566177</v>
+        <v>0.0007994415047217453</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000057722086623</v>
+        <v>1.000000574178089</v>
       </c>
       <c r="O19" t="n">
-        <v>0.008356809099321138</v>
+        <v>0.0008334753846498045</v>
       </c>
       <c r="P19" t="n">
-        <v>157.3054776636001</v>
+        <v>166.5263887727711</v>
       </c>
       <c r="Q19" t="n">
-        <v>241.407909579506</v>
+        <v>250.6288206886769</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_9_3_18</t>
+          <t>model_9_3_6</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9998857909202079</v>
+        <v>0.9999987040084564</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6585373107035681</v>
+        <v>0.6972795048656829</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9992043717774869</v>
+        <v>0.9999997627790431</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9998338591342545</v>
+        <v>0.9999995029895332</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9997499628637656</v>
+        <v>0.9999996706401589</v>
       </c>
       <c r="G20" t="n">
-        <v>6.779944333995538e-05</v>
+        <v>7.693565642211971e-07</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2027070027864974</v>
+        <v>0.1797079627562199</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0003200035450405866</v>
+        <v>1.433041205688111e-07</v>
       </c>
       <c r="J20" t="n">
-        <v>9.161381855840233e-05</v>
+        <v>2.55835205432228e-07</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0002058086817994945</v>
+        <v>1.995696630005195e-07</v>
       </c>
       <c r="L20" t="n">
-        <v>0.003043691126919845</v>
+        <v>0.0003061046959587402</v>
       </c>
       <c r="M20" t="n">
-        <v>0.008234041737807465</v>
+        <v>0.0008771297305536947</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000060911509222</v>
+        <v>1.00000069119549</v>
       </c>
       <c r="O20" t="n">
-        <v>0.008584581941402106</v>
+        <v>0.0009144709590922177</v>
       </c>
       <c r="P20" t="n">
-        <v>157.1979131467535</v>
+        <v>166.1554226046287</v>
       </c>
       <c r="Q20" t="n">
-        <v>241.3003450626594</v>
+        <v>250.2578545205346</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_9_3_19</t>
+          <t>model_9_3_5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9998799479959852</v>
+        <v>0.9999984321329575</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6583138678405791</v>
+        <v>0.6972007343352271</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9991538211792226</v>
+        <v>0.9999997672026973</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9998272296717819</v>
+        <v>0.9999995399441873</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9997353909432637</v>
+        <v>0.9999996884032413</v>
       </c>
       <c r="G21" t="n">
-        <v>7.126805555971989e-05</v>
+        <v>9.307536047698604e-07</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2028396481221968</v>
+        <v>0.1797547243458082</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0003403351147244478</v>
+        <v>1.40631810779819e-07</v>
       </c>
       <c r="J21" t="n">
-        <v>9.526945360869001e-05</v>
+        <v>2.368128665559562e-07</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0002178030111017435</v>
+        <v>1.888064432434644e-07</v>
       </c>
       <c r="L21" t="n">
-        <v>0.003095347126096518</v>
+        <v>0.000332441333217589</v>
       </c>
       <c r="M21" t="n">
-        <v>0.008442040959372319</v>
+        <v>0.0009647557228489813</v>
       </c>
       <c r="N21" t="n">
-        <v>1.000064027735475</v>
+        <v>1.000000836195756</v>
       </c>
       <c r="O21" t="n">
-        <v>0.008801436120446721</v>
+        <v>0.001005827371290325</v>
       </c>
       <c r="P21" t="n">
-        <v>157.0981247191085</v>
+        <v>165.7745425024557</v>
       </c>
       <c r="Q21" t="n">
-        <v>241.2005566350144</v>
+        <v>249.8769744183615</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_9_3_20</t>
+          <t>model_9_3_4</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9998742997438684</v>
+        <v>0.9999980953246558</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6581096636935323</v>
+        <v>0.6971217504634816</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9991056799040202</v>
+        <v>0.9999997704413158</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9998209496517861</v>
+        <v>0.9999995766131319</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9997215273877466</v>
+        <v>0.9999997057318483</v>
       </c>
       <c r="G22" t="n">
-        <v>7.462110200801072e-05</v>
+        <v>1.130697561991993e-06</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2029608725250436</v>
+        <v>0.179801612584002</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0003596976489981872</v>
+        <v>1.386753758070426e-07</v>
       </c>
       <c r="J22" t="n">
-        <v>9.873239820004423e-05</v>
+        <v>2.179375961380071e-07</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0002292142763601825</v>
+        <v>1.783064859725248e-07</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0031438283811893</v>
+        <v>0.0003617923421746257</v>
       </c>
       <c r="M22" t="n">
-        <v>0.008638350653221407</v>
+        <v>0.001063342636214684</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000067040136603</v>
+        <v>1.00000101582685</v>
       </c>
       <c r="O22" t="n">
-        <v>0.009006103124380055</v>
+        <v>0.00110861133366105</v>
       </c>
       <c r="P22" t="n">
-        <v>157.0061744440286</v>
+        <v>165.3853516084021</v>
       </c>
       <c r="Q22" t="n">
-        <v>241.1086063599344</v>
+        <v>249.4877835243079</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_9_3_21</t>
+          <t>model_9_3_3</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9998688819181741</v>
+        <v>0.9999976784998753</v>
       </c>
       <c r="C23" t="n">
-        <v>0.657923223889529</v>
+        <v>0.6970418833268965</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9990600604181478</v>
+        <v>0.9999997752972503</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9998150263105519</v>
+        <v>0.9999996102645666</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9997083967256997</v>
+        <v>0.9999997224461509</v>
       </c>
       <c r="G23" t="n">
-        <v>7.783735737804067e-05</v>
+        <v>1.378142757633218e-06</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2030715512464802</v>
+        <v>0.1798490251663595</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0003780459136638081</v>
+        <v>1.357419275375902e-07</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0001019986620819778</v>
+        <v>2.006155832190516e-07</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0002400222878728929</v>
+        <v>1.681787553783209e-07</v>
       </c>
       <c r="L23" t="n">
-        <v>0.003188984015278745</v>
+        <v>0.0003942224360060904</v>
       </c>
       <c r="M23" t="n">
-        <v>0.008822548236084667</v>
+        <v>0.001173943251453501</v>
       </c>
       <c r="N23" t="n">
-        <v>1.00006992964364</v>
+        <v>1.0000012381334</v>
       </c>
       <c r="O23" t="n">
-        <v>0.009198142379687364</v>
+        <v>0.00122392044606542</v>
       </c>
       <c r="P23" t="n">
-        <v>156.9217781401427</v>
+        <v>164.9895475860736</v>
       </c>
       <c r="Q23" t="n">
-        <v>241.0242100560485</v>
+        <v>249.0919795019794</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_9_3_22</t>
+          <t>model_9_3_2</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9998637261535652</v>
+        <v>0.9999971612841632</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6577535931580762</v>
+        <v>0.6969625036770116</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9990170719278618</v>
+        <v>0.9999997788245311</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9998094687149744</v>
+        <v>0.9999996376021588</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9996960329162965</v>
+        <v>0.9999997357606197</v>
       </c>
       <c r="G24" t="n">
-        <v>8.089804196734241e-05</v>
+        <v>1.685184346862337e-06</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2031722513763366</v>
+        <v>0.1798961483555535</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0003953359857077501</v>
+        <v>1.336111129726076e-07</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0001050632455639729</v>
+        <v>1.865436089350003e-07</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0002501990934211483</v>
+        <v>1.601110927861566e-07</v>
       </c>
       <c r="L24" t="n">
-        <v>0.003231088165648558</v>
+        <v>0.0004323925391927636</v>
       </c>
       <c r="M24" t="n">
-        <v>0.008994333881246704</v>
+        <v>0.001298146504390909</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000072679384765</v>
+        <v>1.00000151398178</v>
       </c>
       <c r="O24" t="n">
-        <v>0.009377241295409259</v>
+        <v>0.001353411288616551</v>
       </c>
       <c r="P24" t="n">
-        <v>156.8446418746316</v>
+        <v>164.5872711909562</v>
       </c>
       <c r="Q24" t="n">
-        <v>240.9470737905375</v>
+        <v>248.6897031068621</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_9_3_23</t>
+          <t>model_9_3_1</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9998588392700617</v>
+        <v>0.9999965195393805</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6575991152337777</v>
+        <v>0.6968854977484681</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9989766622641417</v>
+        <v>0.9999997805931161</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9998042644673354</v>
+        <v>0.999999652465182</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9996844162498056</v>
+        <v>0.9999997430110797</v>
       </c>
       <c r="G25" t="n">
-        <v>8.379910711740444e-05</v>
+        <v>2.066151771810781e-06</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2032639561452991</v>
+        <v>0.1799418624012199</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0004115888476329658</v>
+        <v>1.325427185884683e-07</v>
       </c>
       <c r="J25" t="n">
-        <v>0.00010793298502756</v>
+        <v>1.78892895613272e-07</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0002597609163302629</v>
+        <v>1.557178071008701e-07</v>
       </c>
       <c r="L25" t="n">
-        <v>0.003270201617300452</v>
+        <v>0.0004761245572662576</v>
       </c>
       <c r="M25" t="n">
-        <v>0.009154185224114948</v>
+        <v>0.001437411483121928</v>
       </c>
       <c r="N25" t="n">
-        <v>1.000075285722634</v>
+        <v>1.000001856245664</v>
       </c>
       <c r="O25" t="n">
-        <v>0.009543897840881299</v>
+        <v>0.001498605065810398</v>
       </c>
       <c r="P25" t="n">
-        <v>156.7741764109132</v>
+        <v>164.1796454565895</v>
       </c>
       <c r="Q25" t="n">
-        <v>240.876608326819</v>
+        <v>248.2820773724953</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>model_9_3_24</t>
+          <t>model_9_3_0</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9998542547076322</v>
+        <v>0.9999957252750917</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6574589567649654</v>
+        <v>0.696811305629094</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9989389920843156</v>
+        <v>0.9999997801128251</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9997994367985161</v>
+        <v>0.9999996521749049</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9996735940144973</v>
+        <v>0.9999997426483648</v>
       </c>
       <c r="G26" t="n">
-        <v>8.652070141830573e-05</v>
+        <v>2.537661364058847e-06</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2033471602669166</v>
+        <v>0.179985906048213</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0004267398826837344</v>
+        <v>1.328328602456629e-07</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0001105950704409139</v>
+        <v>1.790423151999369e-07</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0002686688330361395</v>
+        <v>1.559375877227999e-07</v>
       </c>
       <c r="L26" t="n">
-        <v>0.003306175205876603</v>
+        <v>0.0005251744018650293</v>
       </c>
       <c r="M26" t="n">
-        <v>0.009301650467433493</v>
+        <v>0.001593003880741929</v>
       </c>
       <c r="N26" t="n">
-        <v>1.000077730822596</v>
+        <v>1.000002279853284</v>
       </c>
       <c r="O26" t="n">
-        <v>0.009697640984903052</v>
+        <v>0.001660821353917748</v>
       </c>
       <c r="P26" t="n">
-        <v>156.7102536998092</v>
+        <v>163.7685352477418</v>
       </c>
       <c r="Q26" t="n">
-        <v>240.812685615715</v>
+        <v>247.8709671636477</v>
       </c>
     </row>
   </sheetData>
